--- a/lab1/кредиты.xlsx
+++ b/lab1/кредиты.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/princedelen/PycharmProjects/pytorch_test/lab1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/princedelen/PycharmProjects/ai_mathematical_models/lab1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D903C460-63EC-E444-810D-6A4AA0E8F943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2145356A-83DD-B343-85ED-48029D581B25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="27040" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1880" windowWidth="27040" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="loans_demo" sheetId="1" r:id="rId1"/>
@@ -34915,5 +34915,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>